--- a/output/full_scan/batch_seq1_2026-07-30.xlsx
+++ b/output/full_scan/batch_seq1_2026-07-30.xlsx
@@ -4725,7 +4725,7 @@
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>252.4332867065062</v>
+        <v>252.4332867065061</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>16.65</v>
